--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/Луганск/дв 25,08,26 лгрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/Луганск/дв 25,08,26 лгрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\25,08,26 Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\Создание расчетов\ПОКОМ_КИ_UK_Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3712E276-D33D-4744-A77B-CE4DDD4AC24E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224C7179-81A6-4933-ACFF-44EACA001880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,15 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$43</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -413,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -427,7 +419,6 @@
     <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1255,7 +1246,7 @@
       <c r="AE6" s="1">
         <v>0</v>
       </c>
-      <c r="AF6" s="14" t="s">
+      <c r="AF6" s="13" t="s">
         <v>81</v>
       </c>
       <c r="AG6" s="1">
@@ -1616,7 +1607,7 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1652,7 +1643,7 @@
       <c r="R10" s="5">
         <v>24</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S10" s="15">
         <v>0</v>
       </c>
       <c r="T10" s="1" t="e">
@@ -1719,7 +1710,7 @@
       <c r="AX10" s="1"/>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1755,7 +1746,7 @@
       <c r="R11" s="5">
         <v>24</v>
       </c>
-      <c r="S11" s="16">
+      <c r="S11" s="15">
         <v>0</v>
       </c>
       <c r="T11" s="1" t="e">
@@ -1901,7 +1892,7 @@
       <c r="AE12" s="1">
         <v>4.0444000000000004</v>
       </c>
-      <c r="AF12" s="15" t="s">
+      <c r="AF12" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG12" s="1">
@@ -2008,7 +1999,7 @@
       <c r="AE13" s="1">
         <v>0.4</v>
       </c>
-      <c r="AF13" s="14" t="s">
+      <c r="AF13" s="13" t="s">
         <v>53</v>
       </c>
       <c r="AG13" s="1">
@@ -2222,7 +2213,7 @@
       <c r="AE15" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="AF15" s="15" t="s">
+      <c r="AF15" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG15" s="1">
@@ -2882,7 +2873,7 @@
       <c r="AE21" s="1">
         <v>0</v>
       </c>
-      <c r="AF21" s="15" t="s">
+      <c r="AF21" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG21" s="1">
@@ -2987,7 +2978,7 @@
       <c r="AE22" s="1">
         <v>2.4</v>
       </c>
-      <c r="AF22" s="15" t="s">
+      <c r="AF22" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG22" s="1">
@@ -3849,7 +3840,7 @@
       <c r="AE30" s="1">
         <v>9.4</v>
       </c>
-      <c r="AF30" s="15" t="s">
+      <c r="AF30" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG30" s="1">
@@ -3948,7 +3939,7 @@
       <c r="AE31" s="1">
         <v>0</v>
       </c>
-      <c r="AF31" s="15" t="s">
+      <c r="AF31" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG31" s="1">
@@ -4271,7 +4262,7 @@
       <c r="AE34" s="1">
         <v>0.68840000000000001</v>
       </c>
-      <c r="AF34" s="14" t="s">
+      <c r="AF34" s="13" t="s">
         <v>53</v>
       </c>
       <c r="AG34" s="1">
@@ -4376,7 +4367,7 @@
       <c r="AE35" s="1">
         <v>0</v>
       </c>
-      <c r="AF35" s="14" t="s">
+      <c r="AF35" s="13" t="s">
         <v>53</v>
       </c>
       <c r="AG35" s="1">
@@ -4699,7 +4690,7 @@
       <c r="AE38" s="1">
         <v>7.6</v>
       </c>
-      <c r="AF38" s="14" t="s">
+      <c r="AF38" s="13" t="s">
         <v>53</v>
       </c>
       <c r="AG38" s="1">
@@ -4804,7 +4795,7 @@
       <c r="AE39" s="1">
         <v>13.2</v>
       </c>
-      <c r="AF39" s="14" t="s">
+      <c r="AF39" s="13" t="s">
         <v>53</v>
       </c>
       <c r="AG39" s="1">
@@ -5021,7 +5012,7 @@
       <c r="AE41" s="1">
         <v>8.6</v>
       </c>
-      <c r="AF41" s="15" t="s">
+      <c r="AF41" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG41" s="1">
@@ -5220,7 +5211,7 @@
       <c r="AE43" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="AF43" s="15" t="s">
+      <c r="AF43" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AG43" s="1">
